--- a/output/pdf_financials_xlsx/AITT.xlsx
+++ b/output/pdf_financials_xlsx/AITT.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.603849</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.713153</v>
       </c>
     </row>
     <row r="93">
@@ -2672,7 +2672,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.603849</v>
       </c>

--- a/output/pdf_financials_xlsx/AITT.xlsx
+++ b/output/pdf_financials_xlsx/AITT.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.336803</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.075089</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.336803</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.075089</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.345983</v>
+        <v>0.009180000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.084269</v>
+        <v>0.009180000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/AITT.xlsx
+++ b/output/pdf_financials_xlsx/AITT.xlsx
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.035465</v>
       </c>
     </row>
     <row r="111">
@@ -2812,7 +2812,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
